--- a/hourly_load.xlsx
+++ b/hourly_load.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kadekola\github_codes\crossborder-CM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kadekola\github_codes\cross_border-CM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F12FD6-9C37-4312-A88C-C9A6F65796D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC29AF8C-A7BE-44A5-8AC9-3364FE61712D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="1920" windowWidth="16440" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -92,7 +92,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -398,9 +398,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -411,7 +414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45756</v>
       </c>
@@ -425,7 +428,7 @@
         <v>45730.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45756.041666666657</v>
       </c>
@@ -439,7 +442,7 @@
         <v>44302.5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45756.083333333343</v>
       </c>
@@ -453,7 +456,7 @@
         <v>43733.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45756.125</v>
       </c>
@@ -467,7 +470,7 @@
         <v>44037.75</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45756.166666666657</v>
       </c>
@@ -481,7 +484,7 @@
         <v>45518.25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45756.208333333343</v>
       </c>
@@ -495,7 +498,7 @@
         <v>49123.5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45756.25</v>
       </c>
@@ -509,7 +512,7 @@
         <v>55974.75</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45756.291666666657</v>
       </c>
@@ -523,7 +526,7 @@
         <v>60372.5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45756.333333333343</v>
       </c>
@@ -537,7 +540,7 @@
         <v>62953.5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45756.375</v>
       </c>
@@ -551,7 +554,7 @@
         <v>63136.75</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45756.416666666657</v>
       </c>
@@ -565,7 +568,7 @@
         <v>62358</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45756.458333333343</v>
       </c>
@@ -579,7 +582,7 @@
         <v>60182.75</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45756.5</v>
       </c>
@@ -593,7 +596,7 @@
         <v>57910</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45756.541666666657</v>
       </c>
@@ -607,7 +610,7 @@
         <v>56958.25</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45756.583333333343</v>
       </c>
@@ -621,7 +624,7 @@
         <v>55617.5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45756.625</v>
       </c>
@@ -635,7 +638,7 @@
         <v>54837</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45756.666666666657</v>
       </c>
@@ -649,7 +652,7 @@
         <v>54722.5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45756.708333333343</v>
       </c>
@@ -663,7 +666,7 @@
         <v>56516.25</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>45756.75</v>
       </c>
@@ -677,7 +680,7 @@
         <v>59406.25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>45756.791666666657</v>
       </c>
@@ -691,7 +694,7 @@
         <v>59888.25</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>45756.833333333343</v>
       </c>
@@ -705,7 +708,7 @@
         <v>59396.25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>45756.875</v>
       </c>
@@ -719,7 +722,7 @@
         <v>57326</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>45756.916666666657</v>
       </c>
@@ -733,7 +736,7 @@
         <v>53770.75</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45756.958333333343</v>
       </c>
